--- a/public/files/excel/FormatoMovilidades.xlsx
+++ b/public/files/excel/FormatoMovilidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>No.</t>
   </si>
@@ -79,6 +79,9 @@
     <t>UNIDADES TECNOLOGICAS DE SANTANDER
 OFICINA DE RELACIONES INTERINSTITUCIONALES
 REPORTE DE MOVILIDADES</t>
+  </si>
+  <si>
+    <t>Actividad Realizada</t>
   </si>
 </sst>
 </file>
@@ -107,7 +110,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -197,11 +200,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,22 +237,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -654,7 +673,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39.140625" customWidth="1"/>
@@ -664,19 +683,20 @@
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="44.5703125" customWidth="1"/>
     <col min="8" max="8" width="44.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="15" width="18.140625" customWidth="1"/>
-    <col min="16" max="16" width="35.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" customWidth="1"/>
+    <col min="15" max="16" width="18.140625" customWidth="1"/>
+    <col min="17" max="17" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+    <row r="1" spans="1:17" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
       <c r="D1" s="2"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -684,7 +704,7 @@
       <c r="H1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="4"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -692,118 +712,125 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="12"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="11"/>
     </row>
-    <row r="3" spans="1:16" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7"/>
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="5" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <mergeCells count="16">
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
+  <mergeCells count="17">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
